--- a/Requisitos Funcionales (RF)/Requisitos Funcionales (RF) v 0.9/RF11_Costos_OT_v0.9.xlsx
+++ b/Requisitos Funcionales (RF)/Requisitos Funcionales (RF) v 0.9/RF11_Costos_OT_v0.9.xlsx
@@ -543,18 +543,16 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>El sistema debe permitir registrar múltiples costos individuales (con descripción y monto) asociados a una Orden de Trabajo (OT), en lugar de un solo campo de costo adicional. Esto incluye la posibilidad de adjuntar justificaciones documentales (facturas, recibos).</t>
+          <t>Registrar múltiples costos individuales (con descripción y monto) asociados a una OT, en lugar de un solo campo. Incluye adjuntar justificaciones documentales.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>- Registro de Nuevo Costo Adicional (vinculado a una OT)
-- Consulta de Costos Adicionales por OT (tab "Costos" en modal detalle)
-- Edición de Información de Costo Adicional
-- Eliminación de Costo Adicional
-- Subida de Documento Justificativo (reutiliza DocumentoAdjunto con categoria="costo" y ot_costo_id)
-- Cálculo automático del total de costos por OT
-- Reportes RF06: desglose de costos por tipo</t>
+          <t>- CRUD de costos por OT
+- Tab "Costos" en modal detalle
+- Subida de documentos (reutiliza DocumentoAdjunto)
+- Cálculo automático del total
+- Reportes RF06: desglose por tipo</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -564,20 +562,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>VER HOJA "Estructura_Tabla_OtCostoAdicional"</t>
+          <t>VER HOJA "Estructura_OtCostoAdicional"</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>- RF02 (OTs): los costos se asocian a una OT específica
-- RF04 (Repuestos): diferencia costos de repuestos (OtRepuestoUtilizado) de otros costos adicionales
-- RF06 (Reportes): permite cálculos de costos más precisos y detallados
-- RF12 (Contratos): las OTs pueden estar cubiertas por contrato, los costos cubiertos se separan en reportes</t>
+          <t>- RF02 (OTs), RF04 (Repuestos), RF06 (Reportes), RF12 (Contratos)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Mejorar el análisis de costos y la trazabilidad financiera de las actividades de mantenimiento. Permite distinguir claramente entre el costo de los repuestos utilizados y otros gastos asociados a una intervención (transporte, servicios externos, horas de técnico externo, etc.), lo cual es crucial para la evaluación de costos reales de mantenimiento y la toma de decisiones financieras.</t>
+          <t>Mejorar análisis de costos y trazabilidad financiera de mantenimiento.</t>
         </is>
       </c>
     </row>
@@ -622,12 +617,12 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Obligatorio (NOT NULL)</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Valor Predeterminado</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
@@ -667,7 +662,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Identificador único interno del sistema para el registro de costo adicional.</t>
+          <t>Identificador único.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -702,12 +697,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ID de la Orden de Trabajo a la que está asociado este costo (FK a `OrdenTrabajo.id`).</t>
+          <t>FK a OrdenTrabajo.id.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>FK con cascade: si se elimina la OT, se eliminan sus costos</t>
+          <t>Cascade: si se elimina OT, se eliminan costos</t>
         </is>
       </c>
     </row>
@@ -737,12 +732,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Categoría del costo. Dropdown estricto (ver hoja "Valores_Enum_Tipo_Costo").</t>
+          <t>Categoría del costo. Dropdown estricto.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Enum: Transporte, Servicio Externo, Repuesto No Inventariado, Herramienta Renta, Honorarios/Mano de Obra, Insumos/Materiales, Viáticos, Otro</t>
+          <t>Ver hoja "Valores_Enum_Tipo_Costo"</t>
         </is>
       </c>
     </row>
@@ -772,12 +767,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Descripción del concepto del costo (ej. "Transporte técnico al hospital", "Servicio externo de calibración").</t>
+          <t>Descripción del concepto del costo.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Texto libre, permite detalle</t>
+          <t>Texto libre</t>
         </is>
       </c>
     </row>
@@ -807,12 +802,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Monto del costo adicional incurrido.</t>
+          <t>Monto del costo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Número decimal positivo</t>
+          <t>Decimal positivo</t>
         </is>
       </c>
     </row>
@@ -842,7 +837,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Fecha en la que se registró este costo (puede ser la fecha del evento o fecha de registro en sistema).</t>
+          <t>Fecha del costo o de registro.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -877,12 +872,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Username del usuario que registró el costo.</t>
+          <t>Username del usuario.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Para auditoría</t>
+          <t>Auditoría</t>
         </is>
       </c>
     </row>
@@ -912,7 +907,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Fecha y hora en que se creó este registro en el sistema.</t>
+          <t>Fecha de creación en sistema.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -931,7 +926,7 @@
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Se agrega el campo `ot_costo_id` (INTEGER FK opcional) a la tabla `DocumentoAdjunto` existente para vincular documentos justificativos (facturas, recibos) a costos específicos. NO se crea tabla nueva de documentos. Reutiliza toda la lógica existente de subida/descarga/eliminación de DocumentoAdjunto.</t>
+          <t>Se agrega el campo `ot_costo_id` (INTEGER FK opcional) a `DocumentoAdjunto` para vincular documentos justificativos a costos. NO se crea tabla nueva de documentos. Reutiliza toda la lógica existente.</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1200,12 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Agregar soporte para costos asociados directamente a Tareas MP (no solo OTs generadas desde MP).</t>
+          <t>Soporte para costos asociados directamente a Tareas MP.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>Actualmente los costos van solo a OTs. Si una MP tiene costos propios (ej: contrato de servicio), actualmente se crea una OT para registrarlos. Esta opción permitiría registrar costos directamente en la MP.</t>
+          <t>Actualmente los costos van solo a OTs.</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1225,12 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Workflow de aprobación: el técnico registra el costo, el administrador lo aprueba antes de que se compute en reportes.</t>
+          <t>Workflow: técnico registra, administrador aprueba.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Útil para control financiero. Requiere campo `aprobado: bool` y `aprobado_por: str`.</t>
+          <t>Control financiero. Requiere campo aprobado: bool.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1250,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Exportar costos a formato contable (CSV, JSON) para importar en sistema contable del hospital.</t>
+          <t>Exportar costos a formato contable.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1280,12 +1275,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Permitir definir un presupuesto estimado por OT y comparar con costos reales.</t>
+          <t>Definir presupuesto estimado y comparar con costos reales.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Campo `presupuesto_estimado` en OrdenTrabajo. Badge visual si costos reales &gt; presupuesto.</t>
+          <t>Campo presupuesto_estimado en OrdenTrabajo.</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1300,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Generar .meta.json para costos adicionales (similar a equipos, repuestos, herramientas).</t>
+          <t>Generar .meta.json para costos adicionales.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Actualmente NO se genera. El backup/restore JSON ya cubre la BD, así que no es crítico. Útil solo si se quiere recuperar costos sin BD.</t>
+          <t>No crítico, backup/restore JSON ya cubre la BD.</t>
         </is>
       </c>
     </row>
